--- a/Output Data Tables/AFAT Outputs/Aggregated Tables/2019/Airline_Cumulative_Financial_Statistics_2019.xlsx
+++ b/Output Data Tables/AFAT Outputs/Aggregated Tables/2019/Airline_Cumulative_Financial_Statistics_2019.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="44" uniqueCount="44">
   <si>
     <t>Row</t>
   </si>
@@ -85,6 +85,18 @@
   </si>
   <si>
     <t>SkyWest</t>
+  </si>
+  <si>
+    <t>FSC</t>
+  </si>
+  <si>
+    <t>Hybrid</t>
+  </si>
+  <si>
+    <t>ULCC</t>
+  </si>
+  <si>
+    <t>Regional</t>
   </si>
   <si>
     <t>All Airlines</t>
@@ -178,7 +190,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="true"/>
@@ -204,49 +216,49 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
@@ -1404,48 +1416,248 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
+        <v>101338708250</v>
+      </c>
+      <c r="C25" s="0">
+        <v>0.1348</v>
+      </c>
+      <c r="D25" s="0">
+        <v>197.68000000000001</v>
+      </c>
+      <c r="E25" s="0">
+        <v>0.15759999999999999</v>
+      </c>
+      <c r="F25" s="0">
+        <v>232.58000000000001</v>
+      </c>
+      <c r="G25" s="0">
+        <v>109952623610</v>
+      </c>
+      <c r="H25" s="0">
+        <v>0.1462</v>
+      </c>
+      <c r="I25" s="0">
+        <v>214.47999999999999</v>
+      </c>
+      <c r="J25" s="0">
+        <v>0.17100000000000001</v>
+      </c>
+      <c r="K25" s="0">
+        <v>252.34999999999999</v>
+      </c>
+      <c r="L25" s="0">
+        <v>284090</v>
+      </c>
+      <c r="M25" s="0">
+        <v>2646692</v>
+      </c>
+      <c r="N25" s="0">
+        <v>139627</v>
+      </c>
+      <c r="O25" s="0">
+        <v>387034</v>
+      </c>
+      <c r="P25" s="0">
+        <v>18.960000000000001</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0">
+        <v>35422313750</v>
+      </c>
+      <c r="C26" s="0">
+        <v>0.11749999999999999</v>
+      </c>
+      <c r="D26" s="0">
+        <v>111.62</v>
+      </c>
+      <c r="E26" s="0">
+        <v>0.1399</v>
+      </c>
+      <c r="F26" s="0">
+        <v>137.72999999999999</v>
+      </c>
+      <c r="G26" s="0">
+        <v>39802360580</v>
+      </c>
+      <c r="H26" s="0">
+        <v>0.1321</v>
+      </c>
+      <c r="I26" s="0">
+        <v>125.42</v>
+      </c>
+      <c r="J26" s="0">
+        <v>0.15720000000000001</v>
+      </c>
+      <c r="K26" s="0">
+        <v>154.75999999999999</v>
+      </c>
+      <c r="L26" s="0">
+        <v>102037</v>
+      </c>
+      <c r="M26" s="0">
+        <v>2953787</v>
+      </c>
+      <c r="N26" s="0">
+        <v>139942</v>
+      </c>
+      <c r="O26" s="0">
+        <v>390078</v>
+      </c>
+      <c r="P26" s="0">
+        <v>21.109999999999999</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="0">
+        <v>7565399000</v>
+      </c>
+      <c r="C27" s="0">
+        <v>0.081799999999999998</v>
+      </c>
+      <c r="D27" s="0">
+        <v>82.519999999999996</v>
+      </c>
+      <c r="E27" s="0">
+        <v>0.0969</v>
+      </c>
+      <c r="F27" s="0">
+        <v>98.730000000000004</v>
+      </c>
+      <c r="G27" s="0">
+        <v>7969294790</v>
+      </c>
+      <c r="H27" s="0">
+        <v>0.086199999999999999</v>
+      </c>
+      <c r="I27" s="0">
+        <v>86.930000000000007</v>
+      </c>
+      <c r="J27" s="0">
+        <v>0.1021</v>
+      </c>
+      <c r="K27" s="0">
+        <v>104</v>
+      </c>
+      <c r="L27" s="0">
+        <v>19681</v>
+      </c>
+      <c r="M27" s="0">
+        <v>4696868</v>
+      </c>
+      <c r="N27" s="0">
+        <v>106505</v>
+      </c>
+      <c r="O27" s="0">
+        <v>404923</v>
+      </c>
+      <c r="P27" s="0">
+        <v>44.100000000000001</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="0">
+        <v>7976010600</v>
+      </c>
+      <c r="C28" s="0">
+        <v>0.088800000000000004</v>
+      </c>
+      <c r="D28" s="0">
+        <v>44.369999999999997</v>
+      </c>
+      <c r="E28" s="0">
+        <v>0.11119999999999999</v>
+      </c>
+      <c r="F28" s="0">
+        <v>56.32</v>
+      </c>
+      <c r="G28" s="0">
+        <v>8512286630</v>
+      </c>
+      <c r="H28" s="0">
+        <v>0.094799999999999995</v>
+      </c>
+      <c r="I28" s="0">
+        <v>47.359999999999999</v>
+      </c>
+      <c r="J28" s="0">
+        <v>0.1187</v>
+      </c>
+      <c r="K28" s="0">
+        <v>60.109999999999999</v>
+      </c>
+      <c r="L28" s="0">
+        <v>53638</v>
+      </c>
+      <c r="M28" s="0">
+        <v>1674260</v>
+      </c>
+      <c r="N28" s="0">
+        <v>72378</v>
+      </c>
+      <c r="O28" s="0">
+        <v>158699</v>
+      </c>
+      <c r="P28" s="0">
+        <v>23.129999999999999</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="0">
         <v>152302431600</v>
       </c>
-      <c r="C25" s="0">
+      <c r="C29" s="0">
         <v>0.12330000000000001</v>
       </c>
-      <c r="D25" s="0">
+      <c r="D29" s="0">
         <v>138.28</v>
       </c>
-      <c r="E25" s="0">
+      <c r="E29" s="0">
         <v>0.14560000000000001</v>
       </c>
-      <c r="F25" s="0">
+      <c r="F29" s="0">
         <v>167.15000000000001</v>
       </c>
-      <c r="G25" s="0">
+      <c r="G29" s="0">
         <v>166236565610</v>
       </c>
-      <c r="H25" s="0">
+      <c r="H29" s="0">
         <v>0.13450000000000001</v>
       </c>
-      <c r="I25" s="0">
+      <c r="I29" s="0">
         <v>150.93000000000001</v>
       </c>
-      <c r="J25" s="0">
+      <c r="J29" s="0">
         <v>0.15890000000000001</v>
       </c>
-      <c r="K25" s="0">
+      <c r="K29" s="0">
         <v>182.44999999999999</v>
       </c>
-      <c r="L25" s="0">
+      <c r="L29" s="0">
         <v>459446</v>
       </c>
-      <c r="M25" s="0">
+      <c r="M29" s="0">
         <v>2689190</v>
       </c>
-      <c r="N25" s="0">
+      <c r="N29" s="0">
         <v>130428</v>
       </c>
-      <c r="O25" s="0">
+      <c r="O29" s="0">
         <v>361820</v>
       </c>
-      <c r="P25" s="0">
+      <c r="P29" s="0">
         <v>20.620000000000001</v>
       </c>
     </row>
